--- a/Frontend/public/Plantilla_ascenso.xlsx
+++ b/Frontend/public/Plantilla_ascenso.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenne\14-Track\Frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{B5849B2F-2117-459B-BB57-413CB8CD81D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -462,7 +462,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.296875" bestFit="1" customWidth="1"/>
@@ -470,7 +470,7 @@
     <col min="4" max="4" width="13.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="4" t="s">
         <v>8</v>
@@ -482,7 +482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -496,7 +496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -510,7 +510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -524,7 +524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
